--- a/backtest_runs/20260410_193731/by_symbol/TPLI/TPLI.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/TPLI/TPLI.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>108771.85</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>108771.85</v>
@@ -771,7 +771,7 @@
         <v>-90.89999999999806</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>108680.95</v>
@@ -817,7 +817,7 @@
         <v>-90.89999999999806</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>108590.05</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>112180.6</v>
@@ -1139,7 +1139,7 @@
         <v>-545.4000000000045</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>117725.5</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>118952.65</v>
@@ -1323,7 +1323,7 @@
         <v>-4317.749999999996</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>114634.9</v>
@@ -1369,7 +1369,7 @@
         <v>-908.9999999999968</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>113725.9</v>
@@ -1415,7 +1415,7 @@
         <v>-863.5500000000059</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>112862.35</v>
